--- a/terminology/ValueSet-document-category.xlsx
+++ b/terminology/ValueSet-document-category.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -123,19 +123,19 @@
     <t>Lékařské záznamy</t>
   </si>
   <si>
-    <t>11543-6</t>
+    <t>34746-8</t>
   </si>
   <si>
     <t>Ošetřovatelské záznamy</t>
   </si>
   <si>
-    <t>26436-6</t>
+    <t>11502-2</t>
   </si>
   <si>
     <t>Laboratorní nálezy</t>
   </si>
   <si>
-    <t>18726-0</t>
+    <t>85430-7</t>
   </si>
   <si>
     <t>Nálezy zobrazovacího komplementu</t>
